--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>292</v>
+        <v>135</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>103</v>
+        <v>342</v>
       </c>
       <c r="D3">
-        <v>255</v>
+        <v>61</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D3">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
